--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512405_ELIMINATORIAS18FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512405_ELIMINATORIAS18FINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2598</v>
+        <v>6.5503</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0417</v>
+        <v>6.6129</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2181</v>
+        <v>-0.0626</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0422</v>
+        <v>2.0458</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7509</v>
+        <v>1.7777</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2913</v>
+        <v>0.2681</v>
       </c>
       <c r="J2" t="n">
-        <v>3.294</v>
+        <v>3.359</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9779</v>
+        <v>3.0409</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3161</v>
+        <v>0.318</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.2518</v>
+        <v>-1.3131</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.227</v>
+        <v>-1.2633</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0248</v>
+        <v>-0.0499</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S2" t="n">
-        <v>1.808</v>
+        <v>1.0996</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3865</v>
+        <v>0.8736</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4215</v>
+        <v>0.226</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7709</v>
+        <v>1.7853</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3612</v>
+        <v>2.3804</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5903</v>
+        <v>-0.5951</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9207</v>
+        <v>5.3543</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5266</v>
+        <v>4.8832</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3941</v>
+        <v>0.4711</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1052</v>
+        <v>3.1436</v>
       </c>
       <c r="H3" t="n">
-        <v>1.402</v>
+        <v>1.4034</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7032</v>
+        <v>1.7402</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4271</v>
+        <v>3.5044</v>
       </c>
       <c r="K3" t="n">
-        <v>1.932</v>
+        <v>1.9557</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4951</v>
+        <v>1.5487</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3219</v>
+        <v>-0.3608</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5299</v>
+        <v>-0.5523</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2081</v>
+        <v>0.1915</v>
       </c>
       <c r="P3" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2381</v>
+        <v>0.6518</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5091</v>
+        <v>0.7836</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.271</v>
+        <v>-0.1318</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3482</v>
+        <v>0.3442</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5903</v>
+        <v>0.5951</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4849</v>
+        <v>2.6858</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2919</v>
+        <v>2.3713</v>
       </c>
       <c r="F4" t="n">
-        <v>0.193</v>
+        <v>0.3146</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2766</v>
+        <v>-0.2659</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5885</v>
+        <v>0.6116</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8651</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6504</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7004</v>
+        <v>0.7487</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.05</v>
+        <v>-0.0325</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.927</v>
+        <v>-0.9821</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1119</v>
+        <v>-0.1371</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8151</v>
+        <v>-0.845</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3948</v>
+        <v>-0.2262</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0809</v>
+        <v>-0.1057</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3139</v>
+        <v>-0.1205</v>
       </c>
       <c r="V4" t="n">
-        <v>2.9515</v>
+        <v>2.9755</v>
       </c>
       <c r="W4" t="n">
-        <v>2.9515</v>
+        <v>2.9755</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0402</v>
+        <v>0.3744</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1377</v>
+        <v>-0.5545</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0976</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3953</v>
+        <v>1.3838</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7776</v>
+        <v>0.7712</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6177</v>
+        <v>0.6126</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8107</v>
+        <v>1.8476</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6108</v>
+        <v>0.6315</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2</v>
+        <v>1.2161</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4154</v>
+        <v>-0.4638</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1668</v>
+        <v>0.1398</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.6036</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.2776</v>
+        <v>-3.2392</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5676</v>
+        <v>-0.1751</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8515</v>
+        <v>-0.3531</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2839</v>
+        <v>0.178</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>L. SOUMBEY-ALLEY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.06560000000000001</v>
+        <v>0.0835</v>
       </c>
       <c r="E6" t="n">
-        <v>0.187</v>
+        <v>-1.1874</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2527</v>
+        <v>1.2709</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7</v>
+        <v>-2.9251</v>
       </c>
       <c r="I6" t="n">
-        <v>1.77</v>
+        <v>2.8624</v>
       </c>
       <c r="J6" t="n">
-        <v>0.587</v>
+        <v>0.4376</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8355</v>
+        <v>-1.9387</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4225</v>
+        <v>2.3763</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.517</v>
+        <v>-0.5003</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8645</v>
+        <v>-0.9864000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3474</v>
+        <v>0.4861</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.8194</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2291</v>
+        <v>1.4172</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1679</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6485</v>
+        <v>0.3995</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4806</v>
+        <v>0.3541</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4841</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4841</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. SOUMBEY-ALLEY</t>
+          <t>N. DEDOVIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3886</v>
+        <v>0.024</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8185</v>
+        <v>-0.6917</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4299</v>
+        <v>0.7157</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0706</v>
+        <v>-1.0817</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.9157</v>
+        <v>-1.0066</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8451</v>
+        <v>-0.0752</v>
       </c>
       <c r="J7" t="n">
-        <v>0.368</v>
+        <v>-0.1223</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.9674</v>
+        <v>-0.4945</v>
       </c>
       <c r="L7" t="n">
-        <v>2.3354</v>
+        <v>0.3723</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4386</v>
+        <v>-0.9595</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9483</v>
+        <v>-0.512</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5097</v>
+        <v>-0.4474</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6145</v>
+        <v>1.2147</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0485</v>
+        <v>-0.2025</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2965</v>
+        <v>-0.109</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.138</v>
+        <v>-0.367</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4345</v>
+        <v>0.258</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. DEDOVIC</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8827</v>
+        <v>-0.4735</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3459</v>
+        <v>-0.4641</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4632</v>
+        <v>-0.0094</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0614</v>
+        <v>0.08</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.976</v>
+        <v>-1.6812</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0853</v>
+        <v>1.7611</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1669</v>
+        <v>0.6383</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5016</v>
+        <v>-0.7929</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3347</v>
+        <v>1.4312</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8944</v>
+        <v>-0.5584</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4744</v>
+        <v>-0.8883</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.42</v>
+        <v>0.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2291</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2048</v>
+        <v>-2.0245</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4339</v>
+        <v>1.2147</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0504</v>
+        <v>0.7582</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9741</v>
+        <v>0.9221</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.1638</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.5019</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="9">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4384</v>
+        <v>-2.7832</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.2233</v>
+        <v>-4.0487</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7849</v>
+        <v>1.2654</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9043</v>
+        <v>-1.9071</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7022</v>
+        <v>-0.6924</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2021</v>
+        <v>-1.2147</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.205</v>
+        <v>-1.1451</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5623</v>
+        <v>-0.5163</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6427</v>
+        <v>-0.6288</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6993</v>
+        <v>-0.7619</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1399</v>
+        <v>-0.1761</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5593</v>
+        <v>-0.5859</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.8194</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6335</v>
+        <v>0.2778</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4167</v>
+        <v>-0.3324</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0502</v>
+        <v>0.6102</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3482</v>
+        <v>-0.3442</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3482</v>
+        <v>-0.3442</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4669</v>
+        <v>-3.53</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4942</v>
+        <v>-3.5653</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0273</v>
+        <v>0.0353</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2927</v>
+        <v>-1.3125</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4879</v>
+        <v>-0.4939</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8048</v>
+        <v>-0.8186</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3282</v>
+        <v>-1.3053</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7105</v>
+        <v>-0.6928</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6177</v>
+        <v>-0.6126</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0355</v>
+        <v>-0.0071</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2226</v>
+        <v>0.1989</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1871</v>
+        <v>-0.206</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0065</v>
+        <v>-0.0636</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1547</v>
+        <v>-0.2839</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1482</v>
+        <v>0.2204</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9385</v>
+        <v>-0.9393</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8446</v>
+        <v>-5.3831</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8443</v>
+        <v>-2.8941</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0003</v>
+        <v>-2.489</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2477</v>
+        <v>0.2601</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9419</v>
+        <v>-0.9297</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1896</v>
+        <v>1.1898</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8993</v>
+        <v>0.9544</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1735</v>
+        <v>0.2153</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7258</v>
+        <v>0.7391</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6515</v>
+        <v>-0.6943</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1154</v>
+        <v>-1.145</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4639</v>
+        <v>0.4507</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.8679</v>
+        <v>-2.8343</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.097</v>
+        <v>-4.049</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3173</v>
+        <v>0.7618</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6466</v>
+        <v>0.2005</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9639</v>
+        <v>0.5612</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.5418</v>
+        <v>-3.5706</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.5418</v>
+        <v>-3.5706</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.538399999999999</v>
+        <v>2.902500000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8167000000000004</v>
+        <v>0.4616000000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3551</v>
+        <v>2.440900000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2548</v>
+        <v>2.2834</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.2047</v>
+        <v>-3.165</v>
       </c>
       <c r="I12" t="n">
-        <v>5.4596</v>
+        <v>5.4482</v>
       </c>
       <c r="J12" t="n">
-        <v>8.336399999999999</v>
+        <v>8.8848</v>
       </c>
       <c r="K12" t="n">
-        <v>1.817299999999999</v>
+        <v>2.156899999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>6.5192</v>
+        <v>6.727799999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.0814</v>
+        <v>-6.6013</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.0219</v>
+        <v>-5.3218</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0594</v>
+        <v>-1.2795</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.097</v>
+        <v>-4.049</v>
       </c>
       <c r="Q12" t="n">
-        <v>-17.4121</v>
+        <v>-17.2084</v>
       </c>
       <c r="R12" t="n">
-        <v>13.315</v>
+        <v>13.1595</v>
       </c>
       <c r="S12" t="n">
-        <v>3.442</v>
+        <v>3.7288</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2816</v>
+        <v>1.7372</v>
       </c>
       <c r="U12" t="n">
-        <v>2.1604</v>
+        <v>1.9918</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9385999999999988</v>
+        <v>0.9391999999999991</v>
       </c>
       <c r="W12" t="n">
-        <v>6.977499999999999</v>
+        <v>7.047899999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.0389</v>
+        <v>-6.108700000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.645</v>
+        <v>5.4774</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9092</v>
+        <v>6.1942</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2641</v>
+        <v>-0.7168</v>
       </c>
       <c r="G13" t="n">
-        <v>2.1384</v>
+        <v>2.1578</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5382</v>
+        <v>-0.5527</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6765</v>
+        <v>2.7106</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6234</v>
+        <v>3.7312</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2711</v>
+        <v>0.3141</v>
       </c>
       <c r="L13" t="n">
-        <v>3.3523</v>
+        <v>3.4172</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.485</v>
+        <v>-1.5734</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8092</v>
+        <v>-0.8668</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6758</v>
+        <v>-0.7066</v>
       </c>
       <c r="P13" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R13" t="n">
-        <v>2.663</v>
+        <v>2.6319</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6173</v>
+        <v>-0.8124</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4738</v>
+        <v>-0.3463</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1435</v>
+        <v>-0.4661</v>
       </c>
       <c r="V13" t="n">
-        <v>2.4852</v>
+        <v>2.5123</v>
       </c>
       <c r="W13" t="n">
-        <v>3.7839</v>
+        <v>3.8215</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2987</v>
+        <v>-1.3092</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ JIMÉNEZ</t>
+          <t>P. ASO JIMENEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,58 +1501,58 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8782</v>
+        <v>1.2187</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8782</v>
+        <v>-1.1588</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2.3775</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8782</v>
+        <v>0.5308</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8782</v>
+        <v>1.3451</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-0.8143</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8782</v>
+        <v>-0.534</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8782</v>
+        <v>0.7309</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-1.2649</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.0648</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>0.6141</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>0.4507</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.2147</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.2147</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0.5268</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>-0.6248</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.098</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. ASO JIMENEZ</t>
+          <t>J. JIMÉNEZ JIMÉNEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.866</v>
+        <v>0.889</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.4044</v>
+        <v>0.889</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2704</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5516</v>
+        <v>0.889</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3627</v>
+        <v>0.889</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8111</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5528999999999999</v>
+        <v>0.889</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7221</v>
+        <v>0.889</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.275</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1045</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6407</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.2291</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2291</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9147</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8515</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.06320000000000001</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. JIMENEZ JIMENEZ</t>
+          <t>Y. KOLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6976</v>
+        <v>0.4332</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6918</v>
+        <v>-0.6139</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0058</v>
+        <v>1.0471</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2579</v>
+        <v>-2.5181</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7283</v>
+        <v>0.1191</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.9862</v>
+        <v>-2.6372</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0217</v>
+        <v>-1.1221</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4257</v>
+        <v>0.2548</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.404</v>
+        <v>-1.3769</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2796</v>
+        <v>-1.396</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6973</v>
+        <v>-0.1358</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-1.2602</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4097</v>
+        <v>2.6319</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0485</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6388</v>
+        <v>2.6319</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6509</v>
+        <v>-0.6198</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8862</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2353</v>
+        <v>0.0622</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7143</v>
+        <v>0.9393</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8324</v>
+        <v>1.1902</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1181</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. MUÑOZ SAMATAN</t>
+          <t>J. JIMENEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2927</v>
+        <v>0.4106</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2927</v>
+        <v>0.1831</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2927</v>
+        <v>-0.2415</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2927</v>
+        <v>1.739</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-1.9805</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2927</v>
+        <v>1.0918</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2927</v>
+        <v>2.4687</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-1.3769</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-1.3333</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.7297</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.0245</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.6196</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.2698</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.0603</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.727</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.846</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.119</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Y. KOLO</t>
+          <t>D. MUÑOZ SAMATAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2568</v>
+        <v>0.2963</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4518</v>
+        <v>0.2963</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7087</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.5091</v>
+        <v>0.2963</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1281</v>
+        <v>0.2963</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.6372</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1915</v>
+        <v>0.2963</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2125</v>
+        <v>0.2963</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.404</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3176</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0844</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2332</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.663</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.663</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8356</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.441</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6052999999999999</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9385</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1806</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7803</v>
+        <v>-0.2066</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.119</v>
+        <v>-0.3792</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3387</v>
+        <v>0.1726</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9474</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0552</v>
+        <v>0.0215</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8922</v>
+        <v>0.8923</v>
       </c>
       <c r="J19" t="n">
-        <v>3.116</v>
+        <v>3.1665</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0838</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>3.0322</v>
+        <v>3.0684</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1686</v>
+        <v>-2.2527</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0286</v>
+        <v>-0.0766</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.1399</v>
+        <v>-2.1761</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R19" t="n">
-        <v>2.663</v>
+        <v>2.6319</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2</v>
+        <v>-0.5965</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1622</v>
+        <v>-0.509</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0377</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1181</v>
+        <v>-0.119</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1181</v>
+        <v>-0.119</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3005</v>
+        <v>-1.152</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0135</v>
+        <v>0.3937</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2871</v>
+        <v>-1.5457</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9503</v>
+        <v>0.9476</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1874</v>
+        <v>1.1861</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2371</v>
+        <v>-0.2385</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7512</v>
+        <v>1.804</v>
       </c>
       <c r="K20" t="n">
-        <v>1.8012</v>
+        <v>1.8365</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.05</v>
+        <v>-0.0325</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.8565</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6138</v>
+        <v>-0.6504</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1871</v>
+        <v>-0.206</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7462</v>
+        <v>-0.5774</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9825</v>
+        <v>-0.649</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2363</v>
+        <v>0.0716</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.1191</v>
+        <v>-2.1295</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.3612</v>
+        <v>-2.3804</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. COLOM BARRUFET</t>
+          <t>D. MUNOZ SAMATAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5746</v>
+        <v>-1.4182</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3938</v>
+        <v>-2.216</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8192</v>
+        <v>0.7978</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1814</v>
+        <v>-0.7174</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0253</v>
+        <v>0.356</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.2067</v>
+        <v>-1.0734</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.5666</v>
+        <v>-0.534</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4763</v>
+        <v>0.0388</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.0903</v>
+        <v>-0.5728</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3852</v>
+        <v>-0.1834</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5016</v>
+        <v>0.3171</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1164</v>
+        <v>-0.5006</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6145</v>
+        <v>-1.0123</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.0245</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6145</v>
+        <v>1.0123</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0077</v>
+        <v>0.3114</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1728</v>
+        <v>0.3425</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1805</v>
+        <v>-0.0311</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. GATELL SANZ</t>
+          <t>G. COLOM BARRUFET</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7829</v>
+        <v>-1.7191</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.366</v>
+        <v>-2.6636</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.417</v>
+        <v>0.9445</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5701</v>
+        <v>-2.1581</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.5469</v>
+        <v>0.0388</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0232</v>
+        <v>-2.197</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7282</v>
+        <v>-2.532</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8218</v>
+        <v>-0.4557</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0935</v>
+        <v>-2.0763</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8418</v>
+        <v>0.3738</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7251</v>
+        <v>0.4945</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1167</v>
+        <v>-0.1207</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4097</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4339</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>1.9182</v>
+        <v>-0.1683</v>
       </c>
       <c r="T22" t="n">
-        <v>1.3865</v>
+        <v>-0.1316</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5317</v>
+        <v>-0.0367</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.5407</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.5407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. MUNOZ SAMATAN</t>
+          <t>D. ARJOL LOPEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8281</v>
+        <v>-2.4171</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1583</v>
+        <v>-2.0187</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3302</v>
+        <v>-0.3984</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7074</v>
+        <v>0.1951</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3595</v>
+        <v>-0.7312</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0669</v>
+        <v>0.9263</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5528999999999999</v>
+        <v>1.0338</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0253</v>
+        <v>-0.3576</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5782</v>
+        <v>1.3914</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1545</v>
+        <v>-0.8388</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3342</v>
+        <v>-0.3736</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4887</v>
+        <v>-0.4651</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.0242</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.0485</v>
+        <v>-3.0368</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0242</v>
+        <v>1.8221</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0964</v>
+        <v>-0.0883</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4431</v>
+        <v>-0.0158</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5396</v>
+        <v>-0.0725</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.3092</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.3092</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. ARJOL LOPEZ</t>
+          <t>E. GATELL SANZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9083</v>
+        <v>-3.0102</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2202</v>
+        <v>-1.3469</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6881</v>
+        <v>-1.6633</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2126</v>
+        <v>-2.5786</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7275</v>
+        <v>-1.5421</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9401</v>
+        <v>-1.0365</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9906</v>
+        <v>-0.6892</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3925</v>
+        <v>-0.7922</v>
       </c>
       <c r="L24" t="n">
-        <v>1.383</v>
+        <v>0.103</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.778</v>
+        <v>-1.8894</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3351</v>
+        <v>-0.7499</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4429</v>
+        <v>-1.1395</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.2291</v>
+        <v>0.4049</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.0727</v>
+        <v>-1.0123</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8436</v>
+        <v>1.4172</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5931</v>
+        <v>0.7236</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.138</v>
+        <v>0.3545</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4551</v>
+        <v>0.3691</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2987</v>
+        <v>-1.5602</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2987</v>
+        <v>-1.5602</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.538400000000001</v>
+        <v>-1.198</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.355100000000001</v>
+        <v>-2.4408</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8167000000000001</v>
+        <v>1.2429</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.254700000000001</v>
+        <v>-2.2833</v>
       </c>
       <c r="H25" t="n">
-        <v>3.2048</v>
+        <v>3.1649</v>
       </c>
       <c r="I25" t="n">
-        <v>-5.459599999999999</v>
+        <v>-5.4482</v>
       </c>
       <c r="J25" t="n">
-        <v>6.0817</v>
+        <v>6.6013</v>
       </c>
       <c r="K25" t="n">
-        <v>5.022</v>
+        <v>5.321700000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>1.0595</v>
+        <v>1.2797</v>
       </c>
       <c r="M25" t="n">
-        <v>-8.3363</v>
+        <v>-8.884899999999998</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.817</v>
+        <v>-2.1571</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.518999999999999</v>
+        <v>-6.7277</v>
       </c>
       <c r="P25" t="n">
-        <v>4.096900000000001</v>
+        <v>4.0491</v>
       </c>
       <c r="Q25" t="n">
-        <v>-13.315</v>
+        <v>-13.1595</v>
       </c>
       <c r="R25" t="n">
-        <v>17.4119</v>
+        <v>17.2086</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.4419</v>
+        <v>-2.0245</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.1604</v>
+        <v>-1.9917</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.2816</v>
+        <v>-0.03270000000000006</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.9386000000000001</v>
+        <v>-0.9393</v>
       </c>
       <c r="W25" t="n">
-        <v>6.039</v>
+        <v>6.108599999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.977600000000001</v>
+        <v>-7.047899999999999</v>
       </c>
     </row>
   </sheetData>
